--- a/temp/purchase_invoice_INV-0014.xlsx
+++ b/temp/purchase_invoice_INV-0014.xlsx
@@ -53,7 +53,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +70,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FEF3C7"/>
         <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -149,6 +155,24 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -586,7 +610,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>UI-INV-001</t>
+          <t>SUP-INV-998</t>
         </is>
       </c>
     </row>
@@ -598,7 +622,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -622,7 +646,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>PO-001</t>
+          <t>PO-2026-88</t>
         </is>
       </c>
     </row>
@@ -634,7 +658,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Net 30</t>
         </is>
       </c>
     </row>
@@ -646,7 +670,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>
@@ -713,11 +737,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -726,7 +750,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
@@ -801,20 +825,20 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Flour</t>
+          <t>Wheat Flour</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Grocery &amp; Staples</t>
+          <t>Groceries</t>
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
@@ -823,10 +847,10 @@
         </is>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>420</v>
+        <v>45</v>
       </c>
       <c r="H2" s="12" t="n">
         <v>0</v>
@@ -835,46 +859,156 @@
         <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
+        <v>900</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>9876543211</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Grains</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="17" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>Ramesh</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="inlineStr">
+        <is>
+          <t>9876543211</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Cooking Oil</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Oils</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>9876543211</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
         <v>4200</v>
       </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>D Godown 1</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>Ramesh</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>9876543211</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr"/>
-      <c r="C3" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" s="14" t="inlineStr"/>
-      <c r="E3" s="14" t="inlineStr"/>
-      <c r="F3" s="14" t="inlineStr"/>
-      <c r="G3" s="14" t="inlineStr"/>
-      <c r="H3" s="14" t="inlineStr"/>
-      <c r="I3" s="14" t="inlineStr"/>
-      <c r="J3" s="6" t="n">
-        <v>4200</v>
-      </c>
-      <c r="K3" s="14" t="inlineStr"/>
-      <c r="L3" s="14" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="K5" s="20" t="inlineStr"/>
+      <c r="L5" s="20" t="inlineStr"/>
+      <c r="M5" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
